--- a/daily_matches/job_matches_2026-10-16.xlsx
+++ b/daily_matches/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CapCenter</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, USA USA</t>
+          <t>Rochester, MN, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1e91f59b7cddbc</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c0ce292aee499f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analyst – Data Products and AI Enablement</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Penguin Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Cortex, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, MLflow, Docker, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c49e28c5180f66</t>
+          <t>https://www.indeed.com/viewjob?jk=b2d6ad12b2ad9fa3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Data 360)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, Data Lake, Kinesis, Git, Snowflake, Databricks, Kafka</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,102 +554,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144b94b2b27849cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c14d1c35582579f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Security Engineer - Network Edge Security</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>San Francisco Bay Area, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>RAG, Terraform, Snowflake, Databricks, PySpark, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98106ef012e89694</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mettawa, IL, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, XGBoost, LightGBM, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, Kubernetes, CI/CD, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6919e3b23129e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a2527ed3428f545</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SRC, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fairborn, OH, USA USA</t>
+          <t>Lake Mary, FL, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, scikit-learn, S3, MLflow, Docker, Git, Matplotlib</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b110591744e30bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=35f5106dd1d1fe70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer II</t>
+          <t>Software Engineer, ML infrastructure, Core Inference, Level 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Hadoop, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b838de2f7374f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=94abb06242f880ab</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Michelin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Woodburn, IN, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,207 +729,207 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa405c41bf04634</t>
+          <t>https://www.indeed.com/viewjob?jk=7371abe2ae1355a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distinguished Engineer - Systems Architecture</t>
+          <t>Software Engineer, ML Infrastructure, ML Platform Level 5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, PostgreSQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054028efdfece571</t>
+          <t>https://www.indeed.com/viewjob?jk=60d050649af8affd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bradenton, FL, USA USA</t>
+          <t>Peoria, IL, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b7b5f3f48fa593</t>
+          <t>https://www.indeed.com/viewjob?jk=a40b5a1b574129f9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>RFIC Layout &amp; Design Automation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michelin</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Woodburn, IN, USA USA</t>
+          <t>Calabasas, CA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>TensorFlow, PyTorch, scikit-learn, Python, R, C++, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6657184fc98ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f338bcd876b1e03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
+          <t>Finance AI Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Durham, NC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Cortex, CI/CD, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97f5c7eaef0f47d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f93722675d1229</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Prod Sec Engineer - Apps (70008804)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Washington State Hospital Association</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, C++</t>
+          <t>Redshift, Snowflake, Redshift, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e895fe909ac97ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=71bfb22b0a3b241f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Scientist - Flex Pay</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Upgrade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, scikit-learn, PySpark, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,287 +939,42 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee54c8bb60a99024</t>
+          <t>https://www.indeed.com/viewjob?jk=74121efbf4234092</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DigiCert</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OR, USA USA</t>
+          <t>Worcester, MA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, CI/CD, Git, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944109c1f5f09c93</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AppFolio Inc</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97506527ad4f79b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - HMI &amp; AI Systems</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Fairmount Technologies</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Derby, KS, USA USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15d317008737ab21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Application Development Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Intel Corporation</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Hillsboro, OR, USA USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4397e2eb00db15a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Flex Pay</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Upgrade</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, USA USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, scikit-learn, PySpark, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e90502d77185971</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AppFolio Inc</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Goleta, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2eb63a768e3cc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer- Full Stack Web/Mobile</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Resideo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6699464efa1c935e</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>The Hanover Insurance Group</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Git, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=767fb9de2efe563b</t>
+          <t>https://www.indeed.com/viewjob?jk=f28d5e81c858a662</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-16.xlsx
+++ b/daily_matches/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rochester, MN, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, S3, Redshift, BigQuery, Docker, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,24 +484,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c0ce292aee499f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3df57ec03be7e2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penguin Solutions</t>
+          <t>SRC, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Syracuse, NY, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, MLflow, Docker, Kubernetes, Terraform</t>
+          <t>Generative AI, RAG, Hugging Face, PyTorch, scikit-learn, S3, MLflow, Docker, Git, Matplotlib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2d6ad12b2ad9fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=bee52c7d3099a9fe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Research Scientist 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, XGBoost, LightGBM, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c14d1c35582579f</t>
+          <t>https://www.indeed.com/viewjob?jk=24fff9f5909d68af</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Security Engineer - Network Edge Security</t>
+          <t>AI Model Optimization Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, USA USA</t>
+          <t>Santa Clara, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Snowflake, Databricks, PySpark, Kafka, MySQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cd7af563ba184</t>
+          <t>https://www.indeed.com/viewjob?jk=085dcaa1dfeb012c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>PREDICTIVE DATA ANALYST - EMERGENCY APPOINTMENT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>County of Los Angeles</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Orleans, LA, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, Kubernetes, CI/CD, R</t>
+          <t>RAG, Synapse, Git, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2527ed3428f545</t>
+          <t>https://www.indeed.com/viewjob?jk=a92dc1517e7c5503</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS MarTech Developer - Delivery Consultant</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f5106dd1d1fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=79bc28ebdb6acc19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, ML infrastructure, Core Inference, Level 4</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>AppFolio Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,59 +694,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94abb06242f880ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0a953551bef0e3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DATA SCIENTIST - EMERGENCY APPOINTMENT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michelin</t>
+          <t>County of Los Angeles</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Woodburn, IN, USA USA</t>
+          <t>CA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Synapse, Git, Databricks, Tableau, Power BI, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7371abe2ae1355a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f3d90105025537e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, ML Infrastructure, ML Platform Level 5</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d050649af8affd</t>
+          <t>https://www.indeed.com/viewjob?jk=066a9c6c3152f668</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Assoc. Dir, DSCS Digital Technologies, Decision Intelligence (m/f/d)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peoria, IL, USA USA</t>
+          <t>Rahway, NJ, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40b5a1b574129f9</t>
+          <t>https://www.indeed.com/viewjob?jk=198ea0d76a078d8f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RFIC Layout &amp; Design Automation</t>
+          <t>Sr. Specialist, Decision Intelligence (m/f/d)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Calabasas, CA, USA USA</t>
+          <t>Rahway, NJ, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, scikit-learn, Python, R, C++, Scala, Optimization, Bayesian</t>
+          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,147 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f338bcd876b1e03</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Finance AI Analyst</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Intuitive (Intuitive Surgical)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Durham, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Cortex, CI/CD, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f93722675d1229</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Washington State Hospital Association</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Redshift, Snowflake, Redshift, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71bfb22b0a3b241f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Flex Pay</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Upgrade</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tampa, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, scikit-learn, PySpark, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74121efbf4234092</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (REMOTE OR MA BASED)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Hanover Insurance Group</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Worcester, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Git, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f28d5e81c858a662</t>
+          <t>https://www.indeed.com/viewjob?jk=064909ffa08fc1c5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-16.xlsx
+++ b/daily_matches/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Sterling, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Docker, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3df57ec03be7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d46eeb55d14c6a2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SRC, Inc.</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Syracuse, NY, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, PyTorch, scikit-learn, S3, MLflow, Docker, Git, Matplotlib</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, Glue, Athena, Redshift, Data Lake, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee52c7d3099a9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Research Scientist 2</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Louisville, KY, USA USA</t>
+          <t>Virginia Beach, VA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, XGBoost, LightGBM, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24fff9f5909d68af</t>
+          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Model Optimization Engineer</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, C++, Scala, Optimization</t>
+          <t>RAG, Gemini, Redshift, BigQuery, Dataflow, Snowflake, BigQuery, Redshift, Hadoop, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085dcaa1dfeb012c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PREDICTIVE DATA ANALYST - EMERGENCY APPOINTMENT</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>County of Los Angeles</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Git, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Machine Learning Engineer, Hugging Face, TensorFlow, PyTorch, scikit-learn, XGBoost, Azure ML, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,67 +624,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92dc1517e7c5503</t>
+          <t>https://www.indeed.com/viewjob?jk=3eec9ce241b74d23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Balt USA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, C++, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, Cortex, Data Lake, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79bc28ebdb6acc19</t>
+          <t>https://www.indeed.com/viewjob?jk=56fca000ef02466b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AppFolio Inc</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Docker, Git, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Databricks, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0a953551bef0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=992ad5ac530b52a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST - EMERGENCY APPOINTMENT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>County of Los Angeles</t>
+          <t>New Hampshire Mutual Bancorp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, USA USA</t>
+          <t>Concord, NH, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Git, Databricks, Tableau, Power BI, R, Optimization</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f3d90105025537e</t>
+          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066a9c6c3152f668</t>
+          <t>https://www.indeed.com/viewjob?jk=36cc4c2d066dc5e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Assoc. Dir, DSCS Digital Technologies, Decision Intelligence (m/f/d)</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rahway, NJ, USA USA</t>
+          <t>Cockeysville, MD, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, LLaMA, Copilot, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,42 +799,287 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198ea0d76a078d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4eafc6f89ed5b8d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Decision Intelligence (m/f/d)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rahway, NJ, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kinesis, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Java, C++</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, USA USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Edison, NJ, USA USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=257cf3b26e3ac665</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vertafore</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Denver, CO, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FastAPI, Docker, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cea945adbc47cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SW Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Austin, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6702a6c742f751a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bravinth Software Solutions</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Montgomery, AL, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60931ddd14d0f7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hartford, CT, USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=064909ffa08fc1c5</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, MicroStrategy, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5349c91631eca2a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Product Support Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Recorded Future</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Arlington, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b051ffce11813f9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-16.xlsx
+++ b/daily_matches/job_matches_2026-10-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sterling, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, PyTorch, scikit-learn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d46eeb55d14c6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1b0e4f8d04d392</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, Glue, Athena, Redshift, Data Lake, MLflow</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421c23fea92d2957</t>
+          <t>https://www.indeed.com/viewjob?jk=697b06d38d4865a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Prolaio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5469552632d64686</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e6c438a9913e4f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics</t>
+          <t>Senior ERP Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Redshift, BigQuery, Dataflow, Snowflake, BigQuery, Redshift, Hadoop, Tableau</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, Prompt Engineering, PyTorch, scikit-learn, BigQuery, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,19 +589,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7f5b4e74ab50a5</t>
+          <t>https://www.indeed.com/viewjob?jk=56e7755072c220b9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer – Simulation &amp; ML Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -610,11 +610,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Hugging Face, TensorFlow, PyTorch, scikit-learn, XGBoost, Azure ML, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eec9ce241b74d23</t>
+          <t>https://www.indeed.com/viewjob?jk=566f7880814fd925</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Engineer (Agentic AI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Balt USA</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Vienna, VA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,34 +649,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Cortex, Data Lake, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fca000ef02466b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c97830c08a7bad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Databricks, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992ad5ac530b52a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1768a151daf35242</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New Hampshire Mutual Bancorp</t>
+          <t>Amalgamated Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Concord, NH, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, LLaMA, Copilot, MLflow, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013237d4696c82bd</t>
+          <t>https://www.indeed.com/viewjob?jk=45ccb440c099e479</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
+          <t>Machine Learning Engineer, Hugging Face, TensorFlow, PyTorch, scikit-learn, XGBoost, Azure ML, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36cc4c2d066dc5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=52d0493275b643b8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Scientist-Load &amp; Renewable energy forecasting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>RPA INFOTECH INDIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cockeysville, MD, USA USA</t>
+          <t>Juno Beach, FL, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, LLaMA, Copilot, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, scikit-learn, XGBoost, LightGBM, S3, EC2, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4eafc6f89ed5b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec73fd0985d229b0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AID&amp;E - AI Governance &amp; Responsible AI - Senior - Consulting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kinesis, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Java, C++</t>
+          <t>AI Engineer, RAG, AWS SageMaker, MLflow, CI/CD, GitHub Actions, Git, Databricks, Power BI, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3abc7d40fac1d76</t>
+          <t>https://www.indeed.com/viewjob?jk=7623ac8c1f35092b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS MarTech Developer - Delivery Consultant</t>
+          <t>AI Application Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Morrisville, NC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96725a6630248399</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a6f10d10fd63a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Worthington Enterprises</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Edison, NJ, USA USA</t>
+          <t>Columbus, OH, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Cortex, MLflow, Docker, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257cf3b26e3ac665</t>
+          <t>https://www.indeed.com/viewjob?jk=8dfae650e8ca4706</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Gen AI Engineer / Gen AI Developer – Python</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>DHANU GLOBAL ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FastAPI, Docker, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cea945adbc47cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb465301470ac71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>AWS MarTech Developer - Delivery Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6702a6c742f751a2</t>
+          <t>https://www.indeed.com/viewjob?jk=04f878d842549645</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bravinth Software Solutions</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montgomery, AL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, C++, Scala</t>
+          <t>Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60931ddd14d0f7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a9010e42300173ab</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Morrisville, NC, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,42 +1044,392 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5349c91631eca2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4527858607032</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Product Support Solutions Developer</t>
+          <t>Solution Architect, AI &amp; Cloud</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recorded Future</t>
+          <t>Advantage Investigations</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, USA USA</t>
+          <t>Thomasville, NC, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, FastAPI, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34a6901254580e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Solution Engineer (Expansion)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Hadoop, Tableau, MicroStrategy, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02e9257f6a31076a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Copy of Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VYNYL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boise, ID, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a27615322418f29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VYNYL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2ad00a085d385d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HiddenLayer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Austin, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea114a3a02f8b685</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Forward Deployed (Copilot and Azure AI Foundry)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Collectiv LLC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b051ffce11813f9</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Databricks, Power BI, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fceb455ac0dc8354</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mirion</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c43244642217e4b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Buildertrend</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Omaha, NE, USA USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Databricks, BigQuery, MongoDB, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9e10df7e2a6a34c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Knowledge Graph</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Prove</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a55d6e6775972ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Analyst, End User Experience</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Royal Caribbean Group</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Miramar, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47aba8c51545ee17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer II, User Targeting</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, MongoDB, NoSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a82c49fdfef62996</t>
         </is>
       </c>
     </row>
